--- a/output/pdf_financials_xlsx/CUPA.xlsx
+++ b/output/pdf_financials_xlsx/CUPA.xlsx
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.260652</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1.432752</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>2.504132</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>5.254458</v>
       </c>
     </row>
     <row r="11">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">

--- a/output/pdf_financials_xlsx/CUPA.xlsx
+++ b/output/pdf_financials_xlsx/CUPA.xlsx
@@ -817,10 +817,10 @@
         <v>-0.429933</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-2.326031</v>
+        <v>-2.342081</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-2.326031</v>
+        <v>-5.214676</v>
       </c>
     </row>
     <row r="21">
@@ -836,10 +836,10 @@
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>0.01605</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>0.107045</v>
       </c>
     </row>
     <row r="22">
@@ -2320,10 +2320,10 @@
         <v>-0.429933</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-2.326031</v>
+        <v>-2.342081</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-2.326031</v>
+        <v>-5.214676</v>
       </c>
     </row>
     <row r="100">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.204969</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00176</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00176</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.064869</v>
+        <v>-1.066629</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.631065</v>
@@ -4536,7 +4536,11 @@
           <t>Net loss from continued operations $</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -5080,7 +5084,11 @@
           <t>Proceeds from private placement $</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5114,7 +5122,11 @@
           <t>Costs of private placement</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -5794,7 +5806,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="n">
         <v>0.204969</v>
       </c>
@@ -6008,7 +6024,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>-0.00176</v>
       </c>
@@ -6756,7 +6776,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -6790,7 +6814,11 @@
           <t>Income from discontinued operations (note 23)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
